--- a/templates/mau-2.xlsx
+++ b/templates/mau-2.xlsx
@@ -466,7 +466,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="8401050" cy="1200150"/>
+    <xdr:ext cx="9932911" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image4.png"/>
